--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ILLINOIS_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/ILLINOIS_2017.xlsx
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C147">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C200">
@@ -4855,7 +4855,7 @@
         <v>63</v>
       </c>
       <c r="D250">
-        <v>0.0009401301259475915</v>
+        <v>0.0009401301259475916</v>
       </c>
     </row>
     <row r="251">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C361">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C843">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C997">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1058">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1059">
@@ -27373,7 +27373,7 @@
         <v>63</v>
       </c>
       <c r="D1501">
-        <v>0.0009401301259475915</v>
+        <v>0.0009401301259475916</v>
       </c>
     </row>
     <row r="1502">
